--- a/p6_deployment/data/france/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/p6_deployment/data/france/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,78 +434,255 @@
           <t>copiado_avoid_nan</t>
         </is>
       </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>88K4TzrO</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
+          <t>2NocJFqd</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">leonard t 
+  fra </t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>6FKPxxgf</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>vVQcGxl1</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>2ek4VdDB</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
+          <t>ripawyyS</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">delajod w 
+  fra </t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>OpNm82MB</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>zuUcoUwO</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>naJ8SfcU</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
+          <t>0js8u60b</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stinat j 
+  fra </t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>UapruDaf</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>EgvyJSJo</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>8Yk0Wxb5</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
+          <t>SOLVXEbk</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">letexier f 
+  fra </t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>25Wk0Fko</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>8MdrBIUb</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>xObInbrn</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
+          <t>fHYrsJy3</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brisard j 
+  fra </t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>CWxpUrtf</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>tAufB9Mi</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>OKfEmvTu</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
+          <t>M5VGwpVA</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wattellier e 
+  fra </t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>d0X3cO3I</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>AaLVdEGK</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>tnl8UGSH</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
+          <t>jqSiuc6F</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">delajod w 
+  fra </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>SIFtcwDc</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>zuUcoUwO</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>fVodXIra</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
+          <t>zkPwWhT1</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">letexier f 
+  fra </t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>SIFtcwDc</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>8MdrBIUb</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>C6diYbTh</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
+          <t>6ehlLyFq</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lissorgue r 
+  fra </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>UapruDaf</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>YTLwacK1</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
